--- a/02_DIA_inicio_2026_analisis_assets/rbd_9699_colegio-naciones-unidas_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9699_colegio-naciones-unidas_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72A5327E-E3B3-4B06-A7C1-04C5FDB253DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30B547E9-96E3-40AB-8391-E272C9E56AC1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9075741-9343-4E06-9D72-3A2CFD153ACA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D5B15E8-AABB-47A1-9F8C-CC31FF23BC6A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAE42F9D-FFE1-4394-8A52-00476FEC1CF9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{089DDB5A-D121-4917-85D1-33A907FCD3AC}"/>
 </file>